--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Priyasha Shah</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9861494544</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9861494544</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1095,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9861494544</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9861494544</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1113,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.67509</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.67509</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1176,25 +1170,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.34637</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.34636999999999</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -544,18 +544,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -572,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -612,7 +630,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>WiFi 6 Upgrade</t>
+          <t>IPTV Issue</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -628,7 +646,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,10 +701,15 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -671,27 +718,49 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -716,42 +785,42 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1218,6 +1287,218 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 9:52 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367040</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Deepak Babu Bhatta</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Deepak Babu Bhatta</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9860985865</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 09:52:59 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860985865</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 07:30:34 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 09:52:59 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Radha Krishna Temple, Raniban - Hindu temple P7JP+2X5 Radha Krishna Chowk, Yerahity Raniban Rd Nagar</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>9860985865@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CDB647</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h 22m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,14 +528,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -562,18 +562,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="B5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -590,10 +608,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -630,7 +648,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>IPTV Issue</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -646,14 +664,14 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>WiFi 6 Upgrade</t>
+          <t>IPTV Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -669,7 +687,30 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -684,13 +725,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,15 +743,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -718,7 +765,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -727,14 +774,17 @@
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>1</v>
+      <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -743,7 +793,10 @@
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -761,6 +814,9 @@
       </c>
       <c r="D4" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -774,18 +830,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -804,11 +860,11 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -825,7 +881,7 @@
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1354,10 +1410,8 @@
           <t>Deepak Babu Bhatta</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9860985865</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9860985865</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1429,10 +1483,8 @@
           <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH3" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
@@ -1451,10 +1503,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1465,37 +1515,685 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h 22m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:18 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368046</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Sarishma Ranjitkar</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Sarishma Ranjitkar</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9843906185</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:18:26 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9843906185</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 04:03:08 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:18:26 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.67491</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Near Bholachhen Pond, Bhaktapur Durbar Square, Bhaktapur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>sarishmaranjitkar17@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>04:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L37-2</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.431547</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>1d 14h 22m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>18h 15m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:23 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367816</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Chaulagain</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Chaulagain</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9813974696</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9813974696</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:23:25 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.707462</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>near Asan Bazar Chittadhar Marg, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>sc321388@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>07:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.312359</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:22 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367816</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Chaulagain</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Chaulagain</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9813974696</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9813974696</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:02:31 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:23:25 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.707462</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>near Asan Bazar Chittadhar Marg, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>sc321388@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>07:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.312359</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -564,14 +564,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -580,18 +580,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -652,10 +670,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -664,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -687,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -710,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -725,14 +743,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,15 +767,20 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -769,16 +793,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>3</v>
+      <c r="F2" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -791,12 +818,15 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -807,16 +837,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>4</v>
+      <c r="F4" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -830,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1616,10 +1649,8 @@
           <t>Sarishma Ranjitkar</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9843906185</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9843906185</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1654,10 +1685,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.67491</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.67491</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1713,25 +1742,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L37-2</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.431547</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.43154699999999</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1832,10 +1857,8 @@
           <t>Sabin Chaulagain</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9813974696</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9813974696</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1870,10 +1893,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.707462</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.707462</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1929,25 +1950,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.312359</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.312359</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -2048,10 +2065,8 @@
           <t>Sabin Chaulagain</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9813974696</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9813974696</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2086,10 +2101,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.707462</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.707462</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -2145,53 +2158,481 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.312359</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.312359</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>21h 20m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>21h 20m</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>21h 20m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368040</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Hitesh Bajracharya</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Hitesh Bajracharya</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9840302981</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9840302981</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:59:00 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.6736</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Purnachandi Temple,Gabahal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>bajrahitesh06@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>04:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.32107</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>18h 38m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:46 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367937</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Khadgi</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Khadgi</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9818239508</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:34:15 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9841385645</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:34:15 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 10:46:41 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.70844</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>27.70843, 85.31185 Tyoda Asan, Kathmandu  , ASAN tyoda ,Kathmandu Metropolitan ward- 25 , Kathmandu,</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>deepeshgai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>06:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.31179</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>20h 12m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr">
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -909,7 +909,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -2273,10 +2273,8 @@
           <t>Hitesh Bajracharya</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9840302981</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9840302981</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2311,10 +2309,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.6736</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.6736</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2370,25 +2366,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>4,3</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.32107</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.32107000000001</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2479,20 +2471,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Dipesh Khadgi</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9818239508</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9818239508</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2527,10 +2513,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.70844</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.70844</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2586,25 +2570,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>3,8</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.31179</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.31179</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -743,10 +743,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -831,25 +831,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>6</v>
+      <c r="F5" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -863,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -898,7 +920,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -909,7 +931,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -2618,6 +2640,222 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Iptv</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367977</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Rajip Maharjan</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Rajip Maharjan</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841612262</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:04:22 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9861758066</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:05:00 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:04:22 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.67494</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Next to Bhatti Restro, Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>razzeep@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>05:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.31944</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -833,14 +833,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -853,25 +853,47 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>7</v>
+      <c r="F6" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -885,7 +907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -931,10 +953,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="28" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
@@ -2707,10 +2729,8 @@
           <t>Rajip Maharjan</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841612262</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841612262</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2745,10 +2765,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.67494</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.67494</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2804,47 +2822,43 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.31944</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.31944</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>19h 59m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>19h 59m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : Iptv  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
@@ -2853,6 +2867,114 @@
       <c r="AX9" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:22 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr"/>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr"/>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -811,17 +811,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -833,17 +833,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -855,14 +855,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -875,25 +875,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>8</v>
+      <c r="F7" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -907,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -925,7 +947,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -935,7 +957,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -953,7 +975,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -2978,6 +3000,222 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:46 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367964</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Maharjan</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Maharjan</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9802100124</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:46:47 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9802100124</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:56:06 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 11:46:47 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.670745</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Chapat Ganesh Marg, Lalitpur 44600 Near by Patan Sundhara, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>nirazonline@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>06:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L112-6</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.32886</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>20h 50m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -975,7 +975,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -3067,10 +3067,8 @@
           <t>Niraj Maharjan</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9802100124</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9802100124</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3105,10 +3103,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.670745</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.670745</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3164,25 +3160,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L112-6</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.32886</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.32886000000001</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue    has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -906,7 +906,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1</v>
@@ -915,7 +915,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -975,7 +975,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -3208,6 +3208,214 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:28 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367954</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Deshar</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Namrata Deshar</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9823711114</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:28:34 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>LTP9823711114</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:48:22 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 12:28:34 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>B&amp;B Hospital, Gwarko (Baidya &amp; Banskota) - General hospital Lalitpur 44700, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>9866438710@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>07:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB959</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>21h 40m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -975,7 +975,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -3275,10 +3275,8 @@
           <t>Namrata Deshar</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9823711114</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9823711114</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3368,10 +3366,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -3382,7 +3378,7 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -564,14 +564,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -582,14 +582,14 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -598,20 +598,38 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>90.9%</t>
+      <c r="B7" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -670,10 +688,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -682,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -716,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -728,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -743,15 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,20 +786,25 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -796,29 +820,32 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>6</v>
+      <c r="G2" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
@@ -826,8 +853,11 @@
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>1</v>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -843,48 +873,54 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -892,30 +928,61 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>10</v>
+      <c r="G8" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -940,12 +1007,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -975,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -3412,6 +3479,862 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367965</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Gautam</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Gautam</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9801093335</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9801093335</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:56:18 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.73129</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Radha Krishna Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>gshankarbro@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>08:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>CDB382</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.28849</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>22h 19m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 1:13 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367965</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Gautam</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Shankar Gautam</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9801093335</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9801093335</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 02:56:18 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:16:08 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.73129</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Radha Krishna Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>gshankarbro@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>08:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB382</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.28849</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>22h 19m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 1:11 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>no internet connection</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366305</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9849670860</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:11:41 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849670860</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:57:34 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:11:41 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Dhobighat, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>info@megahospital.com.np</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>13:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 14m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 1:10 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>No internet connection</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1366302</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital Pharmacy</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Mega Hospital Pharmacy</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9862483865</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:10:44 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>LTP9862483865</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>11 Oct 2026 10:55:22 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:10:44 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Dhobighat , Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>Megapharmacy@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>13:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 15m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -1042,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -3546,10 +3546,8 @@
           <t>Shankar Gautam</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9801093335</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9801093335</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3584,10 +3582,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.73129</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.73129</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3643,25 +3639,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>CDB382</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.28849</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.28849</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3762,10 +3754,8 @@
           <t>Shankar Gautam</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9801093335</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9801093335</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3800,10 +3790,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.73129</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.73129</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3859,25 +3847,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB382</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.28849</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.28849</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3978,10 +3962,8 @@
           <t>Mega Hospital</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9849670860</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9849670860</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -4053,10 +4035,8 @@
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="AH15" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH15" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
@@ -4075,10 +4055,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -4089,7 +4067,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : no internet connection   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -4190,10 +4168,8 @@
           <t>Mega Hospital Pharmacy</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9862483865</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9862483865</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4265,10 +4241,8 @@
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="AH16" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH16" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
@@ -4287,10 +4261,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -4301,7 +4273,7 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : No internet connection  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -600,14 +600,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -616,20 +616,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>93.3%</t>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>93.8%</t>
         </is>
       </c>
     </row>
@@ -700,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -723,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -734,10 +752,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -761,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -769,8 +787,9 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,10 +820,15 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -829,10 +853,13 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>7</v>
+      <c r="H2" s="6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -856,7 +883,10 @@
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -881,7 +911,10 @@
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -906,7 +939,10 @@
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -931,7 +967,10 @@
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -956,7 +995,10 @@
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -979,10 +1021,13 @@
         <v>1</v>
       </c>
       <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>13</v>
+      <c r="H8" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX16"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1042,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -4307,6 +4352,214 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 1:38 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367871</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Dhrubaraj khanal</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Dhrubaraj khanal</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9840794186</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:38:04 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9840794186</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 01:35:47 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 01:38:04 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Euro School - Middle school Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>drkhanal1972@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>10:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L33-8</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 2m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -4419,10 +4419,8 @@
           <t>Dhrubaraj khanal</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9840794186</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9840794186</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4512,10 +4510,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -4526,7 +4522,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>15</v>
-      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>94.1%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>3</v>
@@ -1027,7 +1027,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -4556,6 +4556,222 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 3:24 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1368039</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Maharjan</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Maharjan</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9802110620</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:57:33 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9802110620</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 03:57:33 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 03:24:47 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.70138</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Near Mata Devi Oil Store, Sitapaila, Nagarjun , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>dinfrnpal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>09:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.28111</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>23h 27m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>23h 27m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -4623,10 +4623,8 @@
           <t>Dinesh Maharjan</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9802110620</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9802110620</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4661,10 +4659,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.70138</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.70138</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4720,25 +4716,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.28111</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.28111</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.4%</t>
         </is>
       </c>
     </row>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
@@ -881,13 +881,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1021,13 +1021,13 @@
         <v>1</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1054,10 +1054,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -4764,6 +4764,222 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 5:09 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>slow internet issue</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1367281</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9841974213</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 05:09:00 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9841974213</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>12 Oct 2026 07:42:47 AM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>13 Oct 2026 05:09:00 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Machhapokhara, Balaju-16,Basantanagar,Nimantrana Guest House &amp; Restaurant,Kathmandu, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>gautmnavraj@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>17:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB036</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 9h 26m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_13_Oct_2026.xlsx
@@ -1087,7 +1087,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -4831,10 +4831,8 @@
           <t>Nimantrana Guest House and Restaurant Pvt Ltd</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9841974213</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9841974213</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4869,10 +4867,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4928,25 +4924,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>CDB036</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
